--- a/SampleLogging/1/student/CuongNHE186494/OverallSummary.xlsx
+++ b/SampleLogging/1/student/CuongNHE186494/OverallSummary.xlsx
@@ -35,6 +35,25 @@
   </x:si>
   <x:si>
     <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TC2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Failed 1 step(s):
+  Stage 3:
+    - Console Output: Text Content Mismatch: Content differs at position 16
+Expected (normalized): Client connected
+A...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TC3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TC4</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -61,12 +80,17 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="1">
@@ -88,15 +112,18 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -110,6 +137,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -415,7 +446,7 @@
     <x:col min="2" max="2" width="7.282054" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="14.567768" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="13.996339" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="10.567768" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="67.424911" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" s="2" customFormat="1">
@@ -449,6 +480,55 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E2" s="1"/>
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D3" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C4" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C5" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="1"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
